--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,8 +920,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129974105</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>96486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,41 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516331</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668692</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,35 +900,1281 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>inslag av gamla tallar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135775340</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135775349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6668702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775349</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135775352</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9423</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516366</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668683</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stående död vårtbjörk, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775352</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129974105</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>inslag av gamla tallar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974105</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135775351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775351</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -930,6 +2182,17 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>135775337</v>
       </c>
       <c r="B7" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135775341</v>
       </c>
       <c r="B8" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135775344</v>
       </c>
       <c r="B9" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135775346</v>
       </c>
       <c r="B10" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135775350</v>
       </c>
       <c r="B11" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135775351</v>
       </c>
       <c r="B12" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135775354</v>
       </c>
       <c r="B13" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135775355</v>
       </c>
       <c r="B14" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129974105</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,41 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516331</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668692</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,35 +900,1281 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>inslag av gamla tallar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135775340</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135775349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6668702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775349</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135775352</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9423</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516366</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668683</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stående död vårtbjörk, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775352</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129974105</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>inslag av gamla tallar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974105</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135775351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775351</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -930,6 +2182,17 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>135775349</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135775352</v>
       </c>
       <c r="B5" t="n">
-        <v>9423</v>
+        <v>9425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>135775337</v>
       </c>
       <c r="B7" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135775341</v>
       </c>
       <c r="B8" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135775344</v>
       </c>
       <c r="B9" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135775346</v>
       </c>
       <c r="B10" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135775350</v>
       </c>
       <c r="B11" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135775351</v>
       </c>
       <c r="B12" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135775354</v>
       </c>
       <c r="B13" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135775355</v>
       </c>
       <c r="B14" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129974105</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,41 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516331</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668692</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,35 +900,1281 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>inslag av gamla tallar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135775340</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135775349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6668702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775349</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135775352</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9425</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516366</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668683</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stående död vårtbjörk, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775352</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129974105</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>inslag av gamla tallar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974105</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135775351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775351</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -930,6 +2182,17 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>135775337</v>
       </c>
       <c r="B7" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135775341</v>
       </c>
       <c r="B8" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135775344</v>
       </c>
       <c r="B9" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135775346</v>
       </c>
       <c r="B10" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135775350</v>
       </c>
       <c r="B11" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135775351</v>
       </c>
       <c r="B12" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135775354</v>
       </c>
       <c r="B13" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135775355</v>
       </c>
       <c r="B14" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129974105</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,41 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516331</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668692</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,35 +900,1281 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>inslag av gamla tallar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135775340</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135775349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6668702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775349</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135775352</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9425</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516366</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668683</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stående död vårtbjörk, lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775352</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129974105</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>inslag av gamla tallar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974105</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135775351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775351</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -930,6 +2182,17 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>135775337</v>
       </c>
       <c r="B7" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135775341</v>
       </c>
       <c r="B8" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135775344</v>
       </c>
       <c r="B9" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135775346</v>
       </c>
       <c r="B10" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135775350</v>
       </c>
       <c r="B11" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135775351</v>
       </c>
       <c r="B12" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135775354</v>
       </c>
       <c r="B13" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135775355</v>
       </c>
       <c r="B14" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>135775337</v>
       </c>
       <c r="B7" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135775341</v>
       </c>
       <c r="B8" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135775344</v>
       </c>
       <c r="B9" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135775346</v>
       </c>
       <c r="B10" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135775350</v>
       </c>
       <c r="B11" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135775351</v>
       </c>
       <c r="B12" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135775354</v>
       </c>
       <c r="B13" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135775355</v>
       </c>
       <c r="B14" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29660-2026 artfynd.xlsx
+++ b/artfynd/A 29660-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>135775337</v>
       </c>
       <c r="B7" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135775341</v>
       </c>
       <c r="B8" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135775344</v>
       </c>
       <c r="B9" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135775346</v>
       </c>
       <c r="B10" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135775350</v>
       </c>
       <c r="B11" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135775351</v>
       </c>
       <c r="B12" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135775354</v>
       </c>
       <c r="B13" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135775355</v>
       </c>
       <c r="B14" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
